--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46201.29166666666</v>
+        <v>46201.08333333334</v>
       </c>
     </row>
     <row r="3">
@@ -837,12 +837,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46201.375</v>
+        <v>46201.13541666666</v>
       </c>
     </row>
     <row r="4">
@@ -996,7 +996,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46201.41666666666</v>
+        <v>46201.29166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46201.5</v>
+        <v>46201.29166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46201.66666666666</v>
+        <v>46201.29166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46201.66666666666</v>
+        <v>46201.33333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46201.66666666666</v>
+        <v>46201.33333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46201.77083333334</v>
+        <v>46201.375</v>
       </c>
     </row>
     <row r="10">
@@ -1950,157 +1950,4450 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>China China League One</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Heilongjiang Lava Spring</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Wuxi Wugou</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>46201.375</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kazakhstan Kazakhstan Premier League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tobol</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Altay</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>46201.41666666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norrby</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46201.41666666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Landskrona</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>46201.41666666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mebrat Hayl</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Awassa Kenema</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n">
+        <v>46201.41666666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sheger Ketema</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mekelakeya</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>46201.41666666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Estonia Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nõmme Kalju</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Paide</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>46201.45833333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EB - Streymur</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>B36</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="3" t="n">
+        <v>46201.45833333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Faroe Islands Faroe Islands Premier League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>KÍ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>07 Vestur</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="3" t="n">
+        <v>46201.45833333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="3" t="n">
+        <v>46201.45833333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="3" t="n">
+        <v>46201.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kazakhstan Kazakhstan Premier League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zhenys</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Astana</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="3" t="n">
+        <v>46201.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lithuania A Lyga</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Banga</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Hegelmann Litauen</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="3" t="n">
+        <v>46201.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lithuania A Lyga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Džiugas Telšiai</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Žalgiris</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" s="3" t="n">
+        <v>46201.53125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Estonia Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Tallinna FC Levadia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tallinna FC Flora</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="3" t="n">
+        <v>46201.54166666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FH</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÍBV</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" s="3" t="n">
+        <v>46201.58333333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Keflavík</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" s="3" t="n">
+        <v>46201.58333333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Thór</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="3" t="n">
+        <v>46201.58333333334</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="3" t="n">
+        <v>46201.58333333334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lithuania A Lyga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Trakai</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kauno Žalgiris</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3" t="n">
+        <v>46201.58333333334</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" s="3" t="n">
+        <v>46201.66666666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" s="3" t="n">
+        <v>46201.66666666666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" s="3" t="n">
+        <v>46201.66666666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Náutico</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" s="3" t="n">
         <v>46201.77083333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="3" t="n">
+        <v>46201.77083333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Supra du Québec</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" s="3" t="n">
+        <v>46201.83333333334</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" s="3" t="n">
+        <v>46201.85416666666</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" s="3" t="n">
+        <v>46201.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.08</v>
+        <v>4.89</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.89</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.08</v>
+        <v>4.89</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>4.89</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,55 +4700,55 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.49</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P27" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,55 +4541,55 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>2.11</v>
       </c>
       <c r="O26" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P26" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>4.89</v>
+        <v>3.88</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.89</v>
+        <v>3.88</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
         <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.88</v>
+        <v>3.08</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.89</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,55 +5018,55 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P29" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
         <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.88</v>
+        <v>3.08</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>4.89</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>3.59</v>
       </c>
       <c r="O26" t="n">
         <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.93</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.89</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.59</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>1.76</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,17 +4696,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>3.59</v>
       </c>
       <c r="O28" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
         <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>3.88</v>
+        <v>3.08</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="O15" t="n">
         <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>3.88</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>3.59</v>
       </c>
       <c r="O27" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.93</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.59</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>2.93</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>2.25</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.89</v>
+        <v>3.88</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,55 +4382,55 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.49</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P25" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.93</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1529,55 +1529,55 @@
         <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1847,55 +1847,55 @@
         <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.88</v>
+        <v>4.89</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="O14" t="n">
         <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.08</v>
+        <v>3.88</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3449,43 +3449,43 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,26 +3746,26 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.7</v>
       </c>
-      <c r="O21" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
@@ -3779,31 +3779,31 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>4.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.1</v>
       </c>
-      <c r="O16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.12</v>
       </c>
-      <c r="AG16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>5.1</v>
+        <v>1.81</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.76</v>
+        <v>1.1</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.39</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3449,43 +3449,43 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.41</v>
       </c>
-      <c r="U20" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.29</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AK20" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.33</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3938,31 +3938,31 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="O27" t="n">
         <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.88</v>
+        <v>4.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,43 +2972,43 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6.76</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.39</v>
+        <v>3.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,43 +3131,43 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="V18" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>5.1</v>
+        <v>1.05</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3461,31 +3461,31 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.33</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.7</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.41</v>
       </c>
-      <c r="U21" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.29</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AK21" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.33</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.49</v>
+        <v>3.59</v>
       </c>
       <c r="O27" t="n">
         <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.25</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.96</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.88</v>
+        <v>4.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.08</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T22" t="n">
         <v>3.35</v>
       </c>
-      <c r="P22" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.59</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>2.82</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.96</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>3.08</v>
+        <v>4.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.89</v>
+        <v>3.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.76</v>
+        <v>1.89</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.39</v>
+        <v>3.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,43 +2972,43 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
-        <v>3.49</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,43 +3131,43 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.81</v>
+        <v>5.1</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>6.76</v>
       </c>
       <c r="O19" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>1.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3461,31 +3461,31 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>5.1</v>
+        <v>1.05</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.7</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.41</v>
-      </c>
       <c r="U20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.29</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z20" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>3.59</v>
       </c>
       <c r="O27" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
         <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,65 +5336,65 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.25</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.96</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
         <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.88</v>
+        <v>3.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>4.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="U15" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.89</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.49</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,43 +2972,43 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.81</v>
+        <v>5.1</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.1</v>
       </c>
-      <c r="O17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.12</v>
       </c>
-      <c r="AG17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>5.1</v>
+        <v>1.81</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6.76</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>1.39</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3461,31 +3461,31 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="O20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.35</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.08</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,19 +4064,19 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -4097,31 +4097,31 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,17 +4696,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.59</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5027,40 +5027,40 @@
         <v>2.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC29" t="n">
         <v>1.79</v>
@@ -5069,13 +5069,13 @@
         <v>1.88</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,65 +5177,65 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,65 +5336,65 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S31" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T31" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.08</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T22" t="n">
         <v>3.35</v>
       </c>
-      <c r="P22" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.59</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P25" t="n">
-        <v>1.76</v>
+        <v>2.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.22</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="S25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T25" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="V25" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z25" t="n">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>3.59</v>
       </c>
       <c r="O27" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,80 +4859,80 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T28" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="U28" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK28" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.46</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="O29" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.22</v>
+        <v>2.65</v>
       </c>
       <c r="R29" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="S29" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T29" t="n">
-        <v>4.5</v>
+        <v>3.82</v>
       </c>
       <c r="U29" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
         <v>1.08</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2.51</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T30" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.05</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE30" t="n">
         <v>1.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,65 +5336,65 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S31" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U31" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S32" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>2.63</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
         <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.88</v>
+        <v>3.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.89</v>
+        <v>3.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.76</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.39</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>6.76</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>1.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3461,31 +3461,31 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.41</v>
       </c>
-      <c r="U21" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.29</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AK21" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.33</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.08</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,43 +4382,43 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>3.49</v>
       </c>
       <c r="O25" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.93</v>
+        <v>1.79</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="S25" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W25" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA25" t="n">
         <v>1.29</v>
@@ -4427,19 +4427,19 @@
         <v>3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>2.11</v>
       </c>
       <c r="O26" t="n">
-        <v>6.25</v>
+        <v>3.88</v>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>2.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.59</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>3.59</v>
       </c>
       <c r="O28" t="n">
         <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="R28" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="S28" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.95</v>
+        <v>1.14</v>
       </c>
       <c r="AK28" t="n">
         <v>1.25</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.51</v>
+        <v>2.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="U30" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
         <v>1.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.75</v>
+        <v>2.39</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.02</v>
+        <v>2.51</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T31" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.05</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE31" t="n">
         <v>1.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.25</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.96</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.65</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.88</v>
+        <v>4.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.49</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>3.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>3.19</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>3.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.89</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T20" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
         <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AA20" t="n">
         <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE20" t="n">
         <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>1.32</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.49</v>
+        <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>3.59</v>
       </c>
       <c r="O27" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
         <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="S28" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T28" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.14</v>
+        <v>1.95</v>
       </c>
       <c r="AK28" t="n">
         <v>1.25</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,65 +5177,65 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T30" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,65 +5495,65 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="R32" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S32" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U32" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
         <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>2.63</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.63</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1688,7 +1688,7 @@
         <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>2.41</v>
@@ -1697,7 +1697,7 @@
         <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
         <v>2.39</v>
@@ -1715,28 +1715,28 @@
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z15" t="n">
         <v>4</v>
       </c>
-      <c r="P15" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>5.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.43</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.49</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.19</v>
+        <v>1.98</v>
       </c>
       <c r="O20" t="n">
-        <v>3.23</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>2.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.44</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="AE20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.25</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>3.19</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>3.23</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.57</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>2.41</v>
+        <v>3.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.28</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>13</v>
+        <v>3.59</v>
       </c>
       <c r="O25" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.11</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>3.88</v>
+        <v>6.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.93</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="O27" t="n">
         <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="S27" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T27" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="V27" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.14</v>
+        <v>1.95</v>
       </c>
       <c r="AK27" t="n">
         <v>1.25</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P28" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="R28" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="S28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.15</v>
       </c>
-      <c r="T28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T29" t="n">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="U29" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="V29" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
         <v>1.08</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.51</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="S31" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="U31" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
         <v>1.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.75</v>
+        <v>2.39</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.02</v>
+        <v>2.51</v>
       </c>
       <c r="R32" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T32" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.05</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE32" t="n">
         <v>1.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.25</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.91</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.05</v>
+        <v>5.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O11" t="n">
-        <v>3.73</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>4.74</v>
+        <v>5.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>4.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>6.76</v>
       </c>
       <c r="O17" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>1.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>5.1</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6.76</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.39</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>1.34</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.61</v>
+        <v>3.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.08</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T22" t="n">
         <v>3.35</v>
       </c>
-      <c r="P22" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.15</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.59</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P25" t="n">
-        <v>1.76</v>
+        <v>2.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.22</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="S25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T25" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="V25" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z25" t="n">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>3.59</v>
       </c>
       <c r="O29" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.93</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.22</v>
+        <v>3.22</v>
       </c>
       <c r="R29" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="S29" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T29" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,65 +5177,65 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.02</v>
+        <v>2.51</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S31" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T31" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.05</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE31" t="n">
         <v>1.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S32" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>3.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.91</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>5.76</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>2.63</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.74</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.4</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="O19" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O20" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.35</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.15</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.19</v>
+        <v>1.96</v>
       </c>
       <c r="O21" t="n">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>3.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="R21" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>3.19</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>3.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>2.39</v>
+        <v>3.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>3.59</v>
       </c>
       <c r="O25" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.93</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>3.22</v>
       </c>
       <c r="R25" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="V25" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,43 +4700,43 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.49</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>2.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="R27" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="S27" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V27" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA27" t="n">
         <v>1.29</v>
@@ -4745,19 +4745,19 @@
         <v>3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
         <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="S29" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T29" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="V29" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.14</v>
+        <v>1.95</v>
       </c>
       <c r="AK29" t="n">
         <v>1.25</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,65 +5177,65 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="R30" t="n">
         <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T30" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="U30" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.51</v>
+        <v>1.91</v>
       </c>
       <c r="R31" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="S31" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T31" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="U31" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U32" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
         <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>2.63</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>4.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.61</v>
+        <v>3.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.08</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.35</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.15</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.59</v>
+        <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>3.59</v>
       </c>
       <c r="O29" t="n">
         <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="R29" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="S29" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T29" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AG29" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.95</v>
+        <v>1.14</v>
       </c>
       <c r="AK29" t="n">
         <v>1.25</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="U30" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.04</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
         <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="R31" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S31" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T31" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE31" t="n">
         <v>1.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>5.4</v>
+        <v>5.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="O3" t="n">
         <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="P4" t="n">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.63</v>
+        <v>3.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>4.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>1.35</v>
@@ -1871,31 +1871,31 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
         <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
         <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
         <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.96</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
         <v>2.3</v>
@@ -2177,7 +2177,7 @@
         <v>3.05</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
         <v>1.49</v>
@@ -2189,7 +2189,7 @@
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
         <v>4</v>
@@ -2207,13 +2207,13 @@
         <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.73</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>4.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>6.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>3.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="R16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.3</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>1.07</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6.76</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.39</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.2</v>
+        <v>1.34</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="S17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.25</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.07</v>
+        <v>7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>3.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.34</v>
+        <v>2.42</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.14</v>
       </c>
-      <c r="T18" t="n">
-        <v>5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="Q20" t="n">
         <v>2.55</v>
       </c>
       <c r="R20" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.36</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF20" t="n">
         <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,22 +3746,22 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.61</v>
+        <v>2.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
         <v>3.35</v>
@@ -3770,7 +3770,7 @@
         <v>2.39</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
         <v>1.08</v>
@@ -3779,16 +3779,16 @@
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>4.47</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
         <v>2.5</v>
@@ -3797,7 +3797,7 @@
         <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF21" t="n">
         <v>1.5</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="S22" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T22" t="n">
         <v>2.44</v>
@@ -3935,7 +3935,7 @@
         <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
         <v>1.43</v>
@@ -3953,7 +3953,7 @@
         <v>3.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
         <v>1.05</v>
@@ -3962,7 +3962,7 @@
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4073,55 +4073,55 @@
         <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="R23" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>4.4</v>
       </c>
       <c r="P24" t="n">
-        <v>5.79</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
         <v>1.94</v>
@@ -4244,22 +4244,22 @@
         <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.46</v>
@@ -4277,10 +4277,10 @@
         <v>1.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>6.25</v>
+        <v>4.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>3.47</v>
       </c>
       <c r="O27" t="n">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.93</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="S27" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="U27" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W27" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB27" t="n">
         <v>3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.97</v>
+        <v>1.23</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
         <v>3.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="R28" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="S28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.2</v>
       </c>
-      <c r="T28" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.7</v>
+        <v>6.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.59</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.22</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.66</v>
       </c>
-      <c r="S29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="R30" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S30" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T30" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="U30" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.05</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
         <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S31" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="U31" t="n">
         <v>2.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
         <v>1.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5507,22 +5507,22 @@
         <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="S32" t="n">
         <v>1.49</v>
       </c>
       <c r="T32" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="U32" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V32" t="n">
         <v>1.28</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
         <v>1.06</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.91</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.76</v>
+        <v>2.84</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="P16" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.2</v>
+        <v>3.68</v>
       </c>
       <c r="R16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>6.76</v>
       </c>
       <c r="O17" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>1.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.34</v>
+        <v>6.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.14</v>
       </c>
-      <c r="T17" t="n">
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
         <v>5</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="O18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R18" t="n">
         <v>3.6</v>
       </c>
-      <c r="P18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.84</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.68</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.5</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.95</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.33</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>3.19</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S21" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>2.39</v>
+        <v>3.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.47</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>2.21</v>
       </c>
       <c r="O22" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>3.38</v>
+        <v>2.39</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.62</v>
+        <v>4.47</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.77</v>
+        <v>2.61</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>2.69</v>
       </c>
       <c r="R25" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="S25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.12</v>
       </c>
-      <c r="T25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.3</v>
       </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.78</v>
+        <v>1.42</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>6.25</v>
+        <v>3.94</v>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.47</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>4.35</v>
+        <v>6.25</v>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>3.13</v>
       </c>
       <c r="O28" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.23</v>
+        <v>3.24</v>
       </c>
       <c r="R28" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="S28" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T28" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V28" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>3.13</v>
       </c>
       <c r="O29" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.33</v>
+        <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>3.84</v>
       </c>
       <c r="R29" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="S29" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T29" t="n">
-        <v>3.96</v>
+        <v>4.8</v>
       </c>
       <c r="U29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V29" t="n">
         <v>2.05</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.71</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z29" t="n">
-        <v>5.2</v>
+        <v>9.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.66</v>
+        <v>3.74</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
         <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R32" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S32" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T32" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
         <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,19 +6290,19 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S37" t="n">
         <v>1.44</v>
@@ -6311,43 +6311,43 @@
         <v>2.47</v>
       </c>
       <c r="U37" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="V37" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.03</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>2.63</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.27</v>
+        <v>2.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="P6" t="n">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="O14" t="n">
-        <v>3.73</v>
+        <v>4.4</v>
       </c>
       <c r="P14" t="n">
-        <v>4.74</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,58 +2792,58 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.15</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
         <v>1.62</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.08</v>
+        <v>7.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.68</v>
+        <v>1.34</v>
       </c>
       <c r="R16" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.95</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.04</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="O18" t="n">
-        <v>7.4</v>
+        <v>3.08</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.34</v>
+        <v>3.68</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>2.95</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>2.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.28</v>
+        <v>2.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>4.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>7</v>
+        <v>1.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.19</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
-        <v>3.38</v>
+        <v>2.39</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.62</v>
+        <v>4.47</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.21</v>
+        <v>3.19</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S22" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>2.39</v>
+        <v>3.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.47</v>
+        <v>2.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,31 +4541,31 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>3.13</v>
       </c>
       <c r="O26" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P26" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="S26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V26" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W26" t="n">
         <v>1.22</v>
@@ -4574,31 +4574,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AD26" t="n">
         <v>1.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,31 +4859,31 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.13</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.24</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W28" t="n">
         <v>1.22</v>
@@ -4892,31 +4892,31 @@
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AD28" t="n">
         <v>1.88</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="R31" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S31" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T31" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
         <v>2.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.05</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE31" t="n">
         <v>1.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S32" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U32" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
         <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>3.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="O13" t="n">
-        <v>3.73</v>
+        <v>4.4</v>
       </c>
       <c r="P13" t="n">
-        <v>4.74</v>
+        <v>5.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4.4</v>
+        <v>3.73</v>
       </c>
       <c r="P14" t="n">
-        <v>5.4</v>
+        <v>4.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>6.76</v>
       </c>
       <c r="O16" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.34</v>
+        <v>6.2</v>
       </c>
       <c r="R16" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.14</v>
       </c>
-      <c r="T16" t="n">
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z16" t="n">
         <v>5</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.07</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6.76</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.39</v>
+        <v>3.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.2</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.5</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.14</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.07</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.08</v>
+        <v>7.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.68</v>
+        <v>1.34</v>
       </c>
       <c r="R18" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.95</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.04</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>3.68</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,77 +3587,77 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="O20" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T20" t="n">
-        <v>2.71</v>
+        <v>3.35</v>
       </c>
       <c r="U20" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.36</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
         <v>1.67</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>3.19</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S21" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>2.39</v>
+        <v>3.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.47</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S22" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.71</v>
       </c>
       <c r="U22" t="n">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.25</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>3.13</v>
       </c>
       <c r="O25" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.69</v>
+        <v>3.84</v>
       </c>
       <c r="R25" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U25" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="V25" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z25" t="n">
-        <v>5.77</v>
+        <v>9.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.63</v>
+        <v>3.74</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.42</v>
+        <v>1.98</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.13</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>3.88</v>
+        <v>6.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>6.25</v>
+        <v>3.95</v>
       </c>
       <c r="P27" t="n">
-        <v>1.11</v>
+        <v>2.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,31 +4859,31 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>3.13</v>
       </c>
       <c r="O28" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P28" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="R28" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="S28" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T28" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V28" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W28" t="n">
         <v>1.22</v>
@@ -4892,31 +4892,31 @@
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AD28" t="n">
         <v>1.88</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.13</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="P29" t="n">
-        <v>1.63</v>
+        <v>3.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.84</v>
+        <v>2.4</v>
       </c>
       <c r="R29" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T29" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="V29" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z29" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,80 +5177,80 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T30" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK30" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="R31" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S31" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="U31" t="n">
         <v>2.95</v>
       </c>
       <c r="V31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.33</v>
       </c>
-      <c r="W31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
         <v>1.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R32" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S32" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T32" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
         <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.81</v>
+        <v>5.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
         <v>2.34</v>
@@ -755,34 +755,34 @@
         <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
         <v>1.14</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="R3" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>2.63</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>3.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="U6" t="n">
-        <v>2.91</v>
+        <v>2.27</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.08</v>
+        <v>5.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,28 +2156,28 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
         <v>1.49</v>
@@ -2189,25 +2189,25 @@
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF11" t="n">
         <v>1.62</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.76</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="P16" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.2</v>
+        <v>3.42</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T16" t="n">
-        <v>3.75</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>2.27</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R17" t="n">
         <v>3.55</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>3.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>4.25</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>3.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.34</v>
+        <v>2.42</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.84</v>
+        <v>6.76</v>
       </c>
       <c r="O19" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>2.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.08</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
         <v>1.67</v>
@@ -3758,7 +3758,7 @@
         <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="S21" t="n">
         <v>1.46</v>
@@ -3785,13 +3785,13 @@
         <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
         <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>4.65</v>
       </c>
       <c r="AD21" t="n">
         <v>1.12</v>
@@ -3803,7 +3803,7 @@
         <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
         <v>1.32</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.28</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4064,16 +4064,16 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
         <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
         <v>2.19</v>
@@ -4085,7 +4085,7 @@
         <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
         <v>1.44</v>
@@ -4097,16 +4097,16 @@
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AA23" t="n">
         <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC23" t="n">
         <v>2.74</v>
@@ -4118,7 +4118,7 @@
         <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG23" t="n">
         <v>2.17</v>
@@ -4223,34 +4223,34 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="O24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>5.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4265,10 +4265,10 @@
         <v>1.46</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
         <v>1.56</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.13</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.84</v>
+        <v>2.64</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="S25" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T25" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.73</v>
       </c>
-      <c r="V25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.95</v>
+        <v>6.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.61</v>
+        <v>1.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.77</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.13</v>
+        <v>3.47</v>
       </c>
       <c r="O28" t="n">
         <v>3.88</v>
@@ -4895,7 +4895,7 @@
         <v>1.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA28" t="n">
         <v>1.33</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="O29" t="n">
         <v>3.94</v>
@@ -5039,7 +5039,7 @@
         <v>4.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="V29" t="n">
         <v>1.85</v>
@@ -5186,49 +5186,49 @@
         <v>3.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="R30" t="n">
         <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF30" t="n">
         <v>2.05</v>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,31 +5336,31 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S31" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T31" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
         <v>1.05</v>
@@ -5369,47 +5369,47 @@
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK31" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="R32" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S32" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="V32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.33</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>2.61</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>4.65</v>
+        <v>4.15</v>
       </c>
       <c r="P35" t="n">
-        <v>8.550000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.23</v>
+        <v>2.71</v>
       </c>
       <c r="R37" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="S37" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T37" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="U37" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="V37" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.04</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE37" t="n">
         <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>2.63</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>2.63</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>6.76</v>
       </c>
       <c r="O16" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.42</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>3.75</v>
       </c>
       <c r="U16" t="n">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>3.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
-        <v>3.55</v>
+        <v>2.21</v>
       </c>
       <c r="S17" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="T17" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.14</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.77</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="P18" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R18" t="n">
         <v>3.55</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.21</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="U18" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.78</v>
+        <v>6.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.03</v>
+        <v>3.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.66</v>
+        <v>1.77</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.83</v>
+        <v>4.25</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6.76</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="P19" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>3.42</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T19" t="n">
-        <v>3.75</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>3.14</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.33</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>3.19</v>
       </c>
       <c r="O20" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
-        <v>2.75</v>
+        <v>3.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.28</v>
+        <v>4.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="S21" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="V21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.25</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>3.95</v>
+        <v>6.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.33</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="P26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.73</v>
       </c>
-      <c r="V26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>1.86</v>
       </c>
       <c r="O27" t="n">
-        <v>6.25</v>
+        <v>3.94</v>
       </c>
       <c r="P27" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.24</v>
+        <v>3.84</v>
       </c>
       <c r="R28" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="S28" t="n">
         <v>1.14</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.55</v>
+        <v>9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.14</v>
+        <v>3.79</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.15</v>
+        <v>1.98</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,31 +5018,31 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.86</v>
+        <v>3.47</v>
       </c>
       <c r="O29" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P29" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="S29" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T29" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.83</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.85</v>
       </c>
       <c r="W29" t="n">
         <v>1.22</v>
@@ -5051,31 +5051,31 @@
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AD29" t="n">
         <v>1.88</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.75</v>
+        <v>2.61</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC32" t="n">
         <v>4.3</v>
       </c>
-      <c r="P32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.61</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.61</v>
+        <v>1.75</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>3.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,58 +2474,58 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.55</v>
       </c>
-      <c r="P13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="U13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.38</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF13" t="n">
         <v>1.62</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,58 +2633,58 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
         <v>1.62</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.87</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.42</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="S19" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="U19" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>2.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.96</v>
+        <v>2.66</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.19</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>3.38</v>
+        <v>2.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.65</v>
+        <v>2.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>3.19</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>2.4</v>
+        <v>3.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>4.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.86</v>
+        <v>13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.94</v>
+        <v>6.25</v>
       </c>
       <c r="P27" t="n">
-        <v>3.25</v>
+        <v>1.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="P28" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.84</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.79</v>
+        <v>3.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5021,10 +5021,10 @@
         <v>3.47</v>
       </c>
       <c r="O29" t="n">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
         <v>3.24</v>
@@ -5054,7 +5054,7 @@
         <v>1.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA29" t="n">
         <v>1.33</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.06</v>
       </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.61</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S31" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="V31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.33</v>
       </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z31" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>2.61</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,61 +6131,61 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S36" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="U36" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE36" t="n">
         <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG36" t="n">
         <v>1.65</v>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,61 +6290,61 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S37" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC37" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE37" t="n">
         <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="n">
         <v>1.65</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.42</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="S17" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="T17" t="n">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="U17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB17" t="n">
         <v>3.14</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AC17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>4.25</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>7.4</v>
+        <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.36</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>4.25</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.19</v>
       </c>
       <c r="O21" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="P21" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="S21" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>2.75</v>
+        <v>3.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.28</v>
+        <v>4.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="S22" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.25</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.84</v>
+        <v>2.64</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="S25" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T25" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.73</v>
       </c>
-      <c r="V25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>3.95</v>
+        <v>6.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.33</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="P27" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="V30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.33</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z30" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>2.61</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC31" t="n">
         <v>4.3</v>
       </c>
-      <c r="P31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.61</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.61</v>
+        <v>1.75</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="R32" t="n">
         <v>2.05</v>
       </c>
       <c r="S32" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T32" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,61 +6131,61 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="R36" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC36" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE36" t="n">
         <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
         <v>1.65</v>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,61 +6290,61 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="R37" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S37" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="U37" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE37" t="n">
         <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
         <v>1.65</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1373,13 +1373,13 @@
         <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.88</v>
@@ -1391,25 +1391,25 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
         <v>1.03</v>
@@ -1418,7 +1418,7 @@
         <v>1.76</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.76</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.39</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T16" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.07</v>
+        <v>4.25</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>3.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
-        <v>3.55</v>
+        <v>2.21</v>
       </c>
       <c r="S17" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="T17" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.14</v>
+        <v>2.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.77</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.44</v>
+        <v>3.75</v>
       </c>
       <c r="U18" t="n">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>3.73</v>
       </c>
       <c r="R19" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>3.02</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.66</v>
+        <v>3.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="S21" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="V21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.25</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>3.94</v>
       </c>
       <c r="R22" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.28</v>
+        <v>3.96</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>3.87</v>
       </c>
       <c r="R23" t="n">
         <v>2.19</v>
@@ -4097,10 +4097,10 @@
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
         <v>1.7</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,80 +4382,80 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="O25" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="P25" t="n">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="S25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U25" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,68 +4537,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="O27" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.84</v>
+        <v>3.24</v>
       </c>
       <c r="R27" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="S27" t="n">
         <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="V27" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.79</v>
+        <v>3.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.98</v>
+        <v>1.15</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,65 +4859,65 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="P28" t="n">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="R28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG28" t="n">
         <v>2.75</v>
       </c>
-      <c r="S28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,68 +5014,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.47</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
-        <v>4.35</v>
+        <v>6.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="R30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2.25</v>
       </c>
-      <c r="S30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2</v>
-      </c>
       <c r="AB30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.61</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.61</v>
+        <v>1.75</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="R31" t="n">
         <v>2.05</v>
       </c>
       <c r="S31" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T31" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="R32" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="V32" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5663,10 +5663,10 @@
         <v>4.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R33" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S33" t="n">
         <v>1.4</v>
@@ -5687,13 +5687,13 @@
         <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
         <v>1.8</v>
@@ -5705,7 +5705,7 @@
         <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF33" t="n">
         <v>1.83</v>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O34" t="n">
         <v>3.3</v>
@@ -6131,16 +6131,16 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="O36" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="R36" t="n">
         <v>2.05</v>
@@ -6152,22 +6152,22 @@
         <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="AA36" t="n">
         <v>2.25</v>
@@ -6176,19 +6176,19 @@
         <v>1.61</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF36" t="n">
         <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6299,16 +6299,16 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S37" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="T37" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U37" t="n">
         <v>3.25</v>
@@ -6317,37 +6317,37 @@
         <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
         <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC37" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE37" t="n">
         <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
         <v>2.7</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="O3" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q3" t="n">
         <v>2.13</v>
@@ -905,7 +905,7 @@
         <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
         <v>1.62</v>
@@ -926,7 +926,7 @@
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC3" t="n">
         <v>2.14</v>
@@ -938,10 +938,10 @@
         <v>1.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.27</v>
+        <v>1.69</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P6" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.7</v>
+        <v>2.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1694,16 +1694,16 @@
         <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
@@ -1712,19 +1712,19 @@
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
         <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
         <v>1.42</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.85</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>6.76</v>
       </c>
       <c r="O16" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>6.31</v>
       </c>
       <c r="R16" t="n">
-        <v>3.55</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.14</v>
+        <v>2.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.25</v>
+        <v>1.05</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
-        <v>3.55</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.42</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2.21</v>
+        <v>2.94</v>
       </c>
       <c r="S17" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="T17" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.78</v>
+        <v>6.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.03</v>
+        <v>3.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.66</v>
+        <v>1.72</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>4.25</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.76</v>
+        <v>2.92</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>3.73</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>3.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>3.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.73</v>
+        <v>2.46</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.44</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
         <v>2.9</v>
@@ -3608,7 +3608,7 @@
         <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
         <v>1.53</v>
@@ -3623,7 +3623,7 @@
         <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
         <v>1.61</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="P21" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>3.94</v>
       </c>
       <c r="R21" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.28</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.94</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="S22" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.96</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>5.79</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
         <v>1.91</v>
@@ -4247,10 +4247,10 @@
         <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4271,7 +4271,7 @@
         <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
         <v>1.18</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.9</v>
+        <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>3.94</v>
+        <v>6.25</v>
       </c>
       <c r="P25" t="n">
-        <v>3.25</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="P26" t="n">
-        <v>1.76</v>
+        <v>2.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.84</v>
+        <v>2.64</v>
       </c>
       <c r="R26" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="S26" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T26" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="V26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.05</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD26" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="P27" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.24</v>
+        <v>3.84</v>
       </c>
       <c r="R27" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="S27" t="n">
         <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.14</v>
+        <v>3.79</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.15</v>
+        <v>1.98</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="O28" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="P28" t="n">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U28" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.63</v>
+        <v>3.16</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,68 +5014,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>3.13</v>
       </c>
       <c r="O29" t="n">
-        <v>6.25</v>
+        <v>3.88</v>
       </c>
       <c r="P29" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R30" t="n">
         <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T30" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.53</v>
+        <v>3.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
         <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="R31" t="n">
         <v>2.05</v>
       </c>
       <c r="S31" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U31" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.05</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE31" t="n">
         <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V32" t="n">
         <v>1.38</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.15</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z34" t="n">
         <v>3.3</v>
       </c>
-      <c r="P34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5975,7 +5975,7 @@
         <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>4.15</v>
+        <v>4.65</v>
       </c>
       <c r="P35" t="n">
         <v>5.5</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U36" t="n">
         <v>3.25</v>
       </c>
-      <c r="P36" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.14</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.55</v>
+        <v>4.95</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="R37" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="S37" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
         <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.95</v>
+        <v>3.55</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O2" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
         <v>1.26</v>
       </c>
       <c r="T2" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
@@ -764,7 +764,7 @@
         <v>4.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
         <v>2.3</v>
@@ -779,10 +779,10 @@
         <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
         <v>2.13</v>
@@ -902,7 +902,7 @@
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
         <v>2.2</v>
@@ -911,7 +911,7 @@
         <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
@@ -926,7 +926,7 @@
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC3" t="n">
         <v>2.14</v>
@@ -938,7 +938,7 @@
         <v>1.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
         <v>2.41</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.7</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
         <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
         </is>
       </c>
       <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AK6" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46201.29166666666</v>
+        <v>46201.33333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>4.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>3.69</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46201.33333333334</v>
+        <v>46201.375</v>
       </c>
     </row>
     <row r="9">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.22</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3.69</v>
+        <v>3.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>3.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.36</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
-        <v>7.4</v>
+        <v>2.85</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.36</v>
+        <v>3.73</v>
       </c>
       <c r="R17" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="T17" t="n">
-        <v>4.2</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>1.88</v>
+        <v>3.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.82</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.27</v>
+        <v>2.13</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.72</v>
+        <v>3.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.73</v>
+        <v>2.46</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.44</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.46</v>
+        <v>1.36</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T19" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.84</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.03</v>
+        <v>3.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.74</v>
+        <v>4.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T21" t="n">
         <v>2.53</v>
@@ -3788,13 +3788,13 @@
         <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
         <v>3.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
         <v>1.01</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="O26" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="P26" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="V26" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="O27" t="n">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="P27" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="S27" t="n">
         <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="V27" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.79</v>
+        <v>3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.98</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,65 +4859,65 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="P28" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="R28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG28" t="n">
         <v>2.75</v>
       </c>
-      <c r="S28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="R29" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="S29" t="n">
         <v>1.14</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>3</v>
+        <v>3.79</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S31" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="R32" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S32" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U32" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.59</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z33" t="n">
         <v>3.3</v>
       </c>
-      <c r="P33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
       <c r="AA33" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>4.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.15</v>
       </c>
-      <c r="S34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="R36" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.95</v>
+        <v>3.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U37" t="n">
         <v>3.25</v>
       </c>
-      <c r="P37" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.14</v>
-      </c>
       <c r="V37" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
         <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.55</v>
+        <v>4.95</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU37"/>
+  <dimension ref="A1:AU45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
         <v>4.55</v>
       </c>
       <c r="P2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
         <v>2.38</v>
@@ -743,13 +743,13 @@
         <v>1.26</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U2" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
@@ -758,31 +758,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
         <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q3" t="n">
         <v>2.13</v>
@@ -902,16 +902,16 @@
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
@@ -926,13 +926,13 @@
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="n">
         <v>1.23</v>
@@ -941,7 +941,7 @@
         <v>1.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
         <v>3.1</v>
@@ -1061,7 +1061,7 @@
         <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
         <v>2.2</v>
@@ -1100,7 +1100,7 @@
         <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.08</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.22</v>
+        <v>4.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
         <v>4.1</v>
@@ -1694,10 +1694,10 @@
         <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
         <v>2.75</v>
@@ -1706,7 +1706,7 @@
         <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
@@ -1718,25 +1718,25 @@
         <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
         <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O9" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P9" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="Q9" t="n">
         <v>2.75</v>
@@ -1853,10 +1853,10 @@
         <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
         <v>2.88</v>
@@ -1874,7 +1874,7 @@
         <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
         <v>2.04</v>
@@ -1883,10 +1883,10 @@
         <v>1.69</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
         <v>1.03</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
         <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
         <v>1.31</v>
@@ -2177,7 +2177,7 @@
         <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
         <v>1.5</v>
@@ -2186,34 +2186,34 @@
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.96</v>
+        <v>4.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
         <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O12" t="n">
         <v>4.4</v>
       </c>
       <c r="P12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.23</v>
@@ -2345,28 +2345,28 @@
         <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AC12" t="n">
         <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF12" t="n">
         <v>1.62</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
         <v>2.75</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.76</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T16" t="n">
         <v>4.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.33</v>
+        <v>3.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.05</v>
+        <v>6.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
         <v>3.73</v>
@@ -3128,7 +3128,7 @@
         <v>1.44</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="U17" t="n">
         <v>3.12</v>
@@ -3143,7 +3143,7 @@
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
         <v>2.88</v>
@@ -3164,10 +3164,10 @@
         <v>1.03</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.46</v>
+        <v>6.31</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AG18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.7</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>1.05</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.36</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>4.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,77 +3587,77 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
         <v>1.67</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
         <v>3.94</v>
@@ -3761,7 +3761,7 @@
         <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T21" t="n">
         <v>2.53</v>
@@ -3770,7 +3770,7 @@
         <v>3.15</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
         <v>1.01</v>
@@ -3788,16 +3788,16 @@
         <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
         <v>3.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF21" t="n">
         <v>1.87</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3.4</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4070,10 +4070,10 @@
         <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
         <v>2.19</v>
@@ -4121,7 +4121,7 @@
         <v>1.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
@@ -4250,7 +4250,7 @@
         <v>1.59</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -4268,10 +4268,10 @@
         <v>2.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE24" t="n">
         <v>1.18</v>
@@ -4296,7 +4296,7 @@
         <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4378,68 +4378,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>6.25</v>
+        <v>4.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="O26" t="n">
         <v>3.94</v>
@@ -4550,25 +4550,25 @@
         <v>3.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
         <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T26" t="n">
         <v>4.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -4577,19 +4577,19 @@
         <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="AC26" t="n">
         <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="n">
         <v>1.35</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="O29" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="P29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.05</v>
       </c>
-      <c r="W29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AD29" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.06</v>
+        <v>13</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>6.25</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>1.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46201.66666666666</v>
+        <v>46201.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.39</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="S31" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="U31" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.55</v>
+        <v>1.77</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,11 +5406,11 @@
         </is>
       </c>
       <c r="AJ31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK31" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AL31" t="n">
         <v>0</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46201.66666666666</v>
+        <v>46201.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -5448,27 +5448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46201.66666666666</v>
+        <v>46201.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -5607,27 +5607,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46201.77083333334</v>
+        <v>46201.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46201.77083333334</v>
+        <v>46201.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -5925,27 +5925,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46201.83333333334</v>
+        <v>46201.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -6084,27 +6084,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46201.85416666666</v>
+        <v>46201.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -6243,156 +6243,1428 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CODM Meknès</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" s="3" t="n">
+        <v>46201.58333333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" s="3" t="n">
+        <v>46201.66666666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P39" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" s="3" t="n">
+        <v>46201.66666666666</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" s="3" t="n">
+        <v>46201.66666666666</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" s="3" t="n">
+        <v>46201.77083333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" s="3" t="n">
+        <v>46201.77083333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Supra du Québec</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" s="3" t="n">
+        <v>46201.83333333334</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Brazil Serie C</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Ypiranga Erechim</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R37" t="n">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.87</v>
       </c>
-      <c r="S37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="S44" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" s="3" t="n">
+        <v>46201.85416666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O45" t="n">
         <v>3.25</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X45" t="n">
         <v>1.02</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y37" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" s="3" t="n">
+      <c r="AF45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" s="3" t="n">
         <v>46201.85416666666</v>
       </c>
     </row>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>2.63</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.54</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.57</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.18</v>
+        <v>4.54</v>
       </c>
       <c r="O9" t="n">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="P9" t="n">
-        <v>3.19</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.75</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.88</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>3.08</v>
       </c>
       <c r="AD9" t="n">
         <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>6.76</v>
       </c>
       <c r="O16" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>6.31</v>
       </c>
       <c r="R16" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="V16" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>6.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.98</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.73</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="S17" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>2.54</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
-        <v>3.12</v>
+        <v>1.81</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.13</v>
+        <v>1.23</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>3.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.88</v>
+        <v>1.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>6.5</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.76</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="P18" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.31</v>
+        <v>3.73</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>2.29</v>
+        <v>3.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>3.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.42</v>
+        <v>3.96</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.94</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.96</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,16 +4382,16 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>3.13</v>
       </c>
       <c r="O25" t="n">
-        <v>4.35</v>
+        <v>3.88</v>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
         <v>2.7</v>
@@ -4400,46 +4400,46 @@
         <v>1.14</v>
       </c>
       <c r="T25" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="V25" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>2.04</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,80 +4541,80 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.03</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>3.94</v>
+        <v>4.35</v>
       </c>
       <c r="P26" t="n">
-        <v>3.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S26" t="n">
         <v>1.14</v>
       </c>
       <c r="T26" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="W26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK26" t="n">
         <v>1.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="O29" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
         <v>1.17</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U29" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="V29" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="W29" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.95</v>
+        <v>7.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.45</v>
+        <v>2.04</v>
       </c>
       <c r="O39" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>7.24</v>
+        <v>3.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="R39" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="S39" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U39" t="n">
-        <v>2.73</v>
+        <v>3.4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="AA39" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="P40" t="n">
-        <v>3.85</v>
+        <v>7.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="S40" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U40" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="V40" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,65 +6926,65 @@
         </is>
       </c>
       <c r="N41" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.85</v>
       </c>
-      <c r="O41" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="O42" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P42" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>4.54</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>3.57</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.54</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>3.57</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>3.52</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
         <v>2.2</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.39</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.51</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
-        <v>3.22</v>
+        <v>3.52</v>
       </c>
       <c r="U14" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
         <v>2.2</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6.76</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T16" t="n">
         <v>4.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.29</v>
+        <v>1.81</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.7</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.05</v>
+        <v>6.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>7.4</v>
+        <v>2.98</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.36</v>
       </c>
-      <c r="R17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>6.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.73</v>
+        <v>2.44</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.44</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AE18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>6.76</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.44</v>
+        <v>6.31</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T19" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.7</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.74</v>
+        <v>1.05</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P20" t="n">
         <v>3.3</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.02</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.94</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>2.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.42</v>
+        <v>3.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
         <v>1.67</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>6.25</v>
+        <v>3.7</v>
       </c>
       <c r="P30" t="n">
-        <v>1.11</v>
+        <v>2.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,17 +6127,17 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6449,16 +6449,16 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O38" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="P38" t="n">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="R38" t="n">
         <v>2.05</v>
@@ -6476,7 +6476,7 @@
         <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
         <v>1.06</v>
@@ -6608,19 +6608,19 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P39" t="n">
-        <v>3.85</v>
+        <v>3.17</v>
       </c>
       <c r="Q39" t="n">
         <v>2.65</v>
       </c>
       <c r="R39" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S39" t="n">
         <v>1.51</v>
@@ -6650,7 +6650,7 @@
         <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC39" t="n">
         <v>4.5</v>
@@ -6767,19 +6767,19 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="O40" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P40" t="n">
-        <v>7.24</v>
+        <v>6.2</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="S40" t="n">
         <v>1.4</v>
@@ -6794,13 +6794,13 @@
         <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
         <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
         <v>3.3</v>
@@ -6818,7 +6818,7 @@
         <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF40" t="n">
         <v>2.15</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P41" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,65 +7085,65 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.85</v>
       </c>
-      <c r="O42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O43" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="P43" t="n">
         <v>6.5</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.48</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.08</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.39</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.54</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
         <v>4.1</v>
@@ -1694,10 +1694,10 @@
         <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U8" t="n">
         <v>2.75</v>
@@ -1706,7 +1706,7 @@
         <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
@@ -1715,13 +1715,13 @@
         <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>3.08</v>
@@ -1733,10 +1733,10 @@
         <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.73</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.44</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AE17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.44</v>
+        <v>6.31</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.7</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>1.05</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6.76</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="P19" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.31</v>
+        <v>3.73</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>2.29</v>
+        <v>3.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.52</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>3.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="O20" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>3.94</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.94</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.83</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.96</v>
+        <v>2.42</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
         <v>1.67</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.85</v>
+        <v>1.94</v>
       </c>
       <c r="O32" t="n">
-        <v>4.35</v>
+        <v>3.65</v>
       </c>
       <c r="P32" t="n">
-        <v>1.63</v>
+        <v>2.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T32" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V32" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>2.04</v>
+        <v>1.21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>3.13</v>
+        <v>3.85</v>
       </c>
       <c r="O35" t="n">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="P35" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="S35" t="n">
         <v>1.14</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="V35" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="W35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>1.22</v>
       </c>
-      <c r="X35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AB35" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.17</v>
+        <v>2.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,68 +6127,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>13</v>
+        <v>3.13</v>
       </c>
       <c r="O36" t="n">
-        <v>6.25</v>
+        <v>3.88</v>
       </c>
       <c r="P36" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="O38" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="P38" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="R38" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S38" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="T38" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="U38" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X38" t="n">
         <v>1.05</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE38" t="n">
         <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O39" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="P39" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R39" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S39" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T39" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="U39" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V39" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
         <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,61 +7403,61 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="R44" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="S44" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="T44" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.25</v>
       </c>
-      <c r="U44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AB44" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="n">
         <v>1.7</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,61 +7562,61 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="R45" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="S45" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.46</v>
       </c>
-      <c r="T45" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U45" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X45" t="n">
+      <c r="AC45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y45" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG45" t="n">
         <v>1.7</v>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="O2" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="Q2" t="n">
         <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
         <v>1.26</v>
@@ -758,28 +758,28 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
         <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
         <v>1.9</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>1.62</v>
       </c>
       <c r="O3" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
         <v>2.13</v>
@@ -905,13 +905,13 @@
         <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
@@ -926,19 +926,19 @@
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
         <v>1.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
         <v>2.45</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>2.63</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>2.95</v>
@@ -1397,7 +1397,7 @@
         <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
         <v>1.62</v>
@@ -1406,10 +1406,10 @@
         <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
         <v>1.15</v>
@@ -1529,22 +1529,22 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
@@ -1556,16 +1556,16 @@
         <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
         <v>1.17</v>
@@ -1574,10 +1574,10 @@
         <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.85</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="P12" t="n">
-        <v>4.9</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.36</v>
       </c>
-      <c r="R16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>6.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.87</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T17" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.74</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.76</v>
+        <v>3.87</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P18" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.31</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="U18" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>1.08</v>
       </c>
       <c r="O19" t="n">
-        <v>2.98</v>
+        <v>7.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.73</v>
+        <v>1.34</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>3.52</v>
       </c>
       <c r="S19" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="T19" t="n">
-        <v>2.54</v>
+        <v>4.75</v>
       </c>
       <c r="U19" t="n">
-        <v>3.12</v>
+        <v>1.81</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>7.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.88</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>2.03</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>6.55</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.28</v>
+        <v>1.96</v>
       </c>
       <c r="O20" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.94</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
         <v>1.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
         <v>2.38</v>
@@ -3770,16 +3770,16 @@
         <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
         <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
         <v>4.5</v>
@@ -3797,7 +3797,7 @@
         <v>1.51</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
         <v>1.5</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>3.94</v>
       </c>
       <c r="R22" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4073,10 +4073,10 @@
         <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="S23" t="n">
         <v>1.28</v>
@@ -4094,13 +4094,13 @@
         <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA23" t="n">
         <v>1.7</v>
@@ -4115,13 +4115,13 @@
         <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
         <v>1.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,16 +4223,16 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R24" t="n">
         <v>2.46</v>
@@ -4244,22 +4244,22 @@
         <v>3.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.46</v>
@@ -4268,10 +4268,10 @@
         <v>2.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
         <v>1.18</v>
@@ -4296,7 +4296,7 @@
         <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.94</v>
+        <v>3.9</v>
       </c>
       <c r="O32" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.53</v>
+        <v>1.77</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="R32" t="n">
         <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="V32" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6455,7 +6455,7 @@
         <v>2.87</v>
       </c>
       <c r="P38" t="n">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="Q38" t="n">
         <v>2.65</v>
@@ -6497,7 +6497,7 @@
         <v>4.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE38" t="n">
         <v>1.03</v>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>1.95</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6767,19 +6767,19 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="O40" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P40" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="S40" t="n">
         <v>1.4</v>
@@ -6788,7 +6788,7 @@
         <v>2.8</v>
       </c>
       <c r="U40" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V40" t="n">
         <v>1.38</v>
@@ -6800,19 +6800,19 @@
         <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA40" t="n">
         <v>2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD40" t="n">
         <v>1.25</v>
@@ -6824,7 +6824,7 @@
         <v>2.15</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6932,7 +6932,7 @@
         <v>3.35</v>
       </c>
       <c r="P41" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O42" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q42" t="n">
         <v>2.38</v>
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V43" t="n">
         <v>1.43</v>
       </c>
-      <c r="O43" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA43" t="n">
         <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O44" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="R44" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S44" t="n">
         <v>1.46</v>
       </c>
       <c r="T44" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="U44" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="V44" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="AD44" t="n">
         <v>1.17</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF44" t="n">
         <v>2</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>1.24</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7571,55 +7571,55 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R45" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S45" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U45" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
         <v>1.07</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE45" t="n">
         <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.13</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>2.85</v>
+        <v>4.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>5.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.38</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>4.65</v>
+        <v>2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>5.93</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>3.87</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.4</v>
+        <v>1.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.44</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
         <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.74</v>
+        <v>1.12</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.82</v>
+        <v>1.08</v>
       </c>
       <c r="O17" t="n">
-        <v>2.95</v>
+        <v>7.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>1.34</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>3.52</v>
       </c>
       <c r="S17" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="U17" t="n">
-        <v>3.12</v>
+        <v>1.81</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="W17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.04</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.87</v>
+        <v>1.83</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.58</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>2.44</v>
       </c>
       <c r="R18" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="U18" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
         <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.06</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.08</v>
+        <v>2.82</v>
       </c>
       <c r="O19" t="n">
-        <v>7.4</v>
+        <v>2.95</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.34</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>3.52</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.81</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>6.55</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,31 +4382,31 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.47</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="P25" t="n">
-        <v>1.69</v>
+        <v>2.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.11</v>
+        <v>2.5</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S25" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T25" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="W25" t="n">
         <v>1.22</v>
@@ -4415,31 +4415,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.19</v>
+        <v>1.69</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,31 +5018,31 @@
         </is>
       </c>
       <c r="N29" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.95</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.8</v>
-      </c>
       <c r="V29" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="W29" t="n">
         <v>1.22</v>
@@ -5051,31 +5051,31 @@
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>7.3</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF29" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AG29" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="O32" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="P32" t="n">
-        <v>1.77</v>
+        <v>5.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.95</v>
+        <v>2.11</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="S32" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="T32" t="n">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="U32" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.99</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.56</v>
+        <v>3.04</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.6</v>
+        <v>1.76</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>3.63</v>
+        <v>2.62</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.94</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
-        <v>2.87</v>
+        <v>4.05</v>
       </c>
       <c r="P38" t="n">
-        <v>3.78</v>
+        <v>6.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="S38" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z38" t="n">
         <v>3.4</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.53</v>
-      </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.72</v>
+        <v>2.79</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,80 +6767,80 @@
         </is>
       </c>
       <c r="N40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.32</v>
       </c>
-      <c r="O40" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK40" t="n">
-        <v>2.79</v>
+        <v>1.72</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-06-28.xlsx
+++ b/jogos_2026-06-28.xlsx
@@ -728,13 +728,13 @@
         <v>1.38</v>
       </c>
       <c r="O2" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P2" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>2.5</v>
@@ -743,10 +743,10 @@
         <v>1.26</v>
       </c>
       <c r="T2" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V2" t="n">
         <v>1.5</v>
@@ -758,16 +758,16 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
         <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
         <v>2.41</v>
@@ -779,10 +779,10 @@
         <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
@@ -926,13 +926,13 @@
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="n">
         <v>1.23</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
         <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="R4" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="S4" t="n">
         <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
         <v>2.2</v>
@@ -1100,7 +1100,7 @@
         <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.08</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.44</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.68</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>4.13</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>3.02</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.75</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.02</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>5.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.44</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>3.52</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.92</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
         <v>2.2</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.87</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.58</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
         <v>4.33</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AA16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
         <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.08</v>
+        <v>2.82</v>
       </c>
       <c r="O17" t="n">
-        <v>7.4</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.34</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>3.52</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="T17" t="n">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.81</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.83</v>
+        <v>1.08</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.44</v>
+        <v>1.34</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>3.52</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="T18" t="n">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z18" t="n">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.82</v>
+        <v>3.87</v>
       </c>
       <c r="O19" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="S19" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>3.38</v>
       </c>
       <c r="U19" t="n">
-        <v>3.12</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.88</v>
+        <v>2.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>3.28</v>
       </c>
       <c r="O21" t="n">
-        <v>3.48</v>
+        <v>3.29</v>
       </c>
       <c r="P21" t="n">
-        <v>2.95</v>
+        <v>2.19</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>3.94</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.33</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W21" t="n">